--- a/artfynd/A 9959-2026 artfynd.xlsx
+++ b/artfynd/A 9959-2026 artfynd.xlsx
@@ -1054,7 +1054,7 @@
         <v>131273746</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>131273722</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9959-2026 artfynd.xlsx
+++ b/artfynd/A 9959-2026 artfynd.xlsx
@@ -1054,7 +1054,7 @@
         <v>131273746</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>131273722</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9959-2026 artfynd.xlsx
+++ b/artfynd/A 9959-2026 artfynd.xlsx
@@ -1054,7 +1054,7 @@
         <v>131273746</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>131273722</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9959-2026 artfynd.xlsx
+++ b/artfynd/A 9959-2026 artfynd.xlsx
@@ -675,68 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100764566</v>
+        <v>112215602</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5685</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>O Simsbodarna, Dlr</t>
+          <t>Simsbodarna , Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515306</v>
+        <v>515159</v>
       </c>
       <c r="R2" t="n">
-        <v>6705058</v>
+        <v>6705040</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-13</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-13</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,54 +783,63 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112215602</v>
+        <v>100764566</v>
       </c>
       <c r="B3" t="n">
-        <v>89006</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Simsbodarna , Dlr</t>
+          <t>O Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515159</v>
+        <v>515306</v>
       </c>
       <c r="R3" t="n">
-        <v>6705039</v>
+        <v>6705058</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,22 +863,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2022-05-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2022-05-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,77 +905,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115904308</v>
+        <v>131273722</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster om Simsbodarna, Dlr</t>
+          <t>Sims fäbodar, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515446</v>
+        <v>515365</v>
       </c>
       <c r="R4" t="n">
-        <v>6705174</v>
+        <v>6705054</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,22 +978,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,12 +1003,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil Alexandersson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emil Alexandersson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1054,7 +1018,7 @@
         <v>131273746</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,56 +1125,72 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131273722</v>
+        <v>115904308</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sims fäbodar, Dlr</t>
+          <t>Öster om Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515365</v>
+        <v>515446</v>
       </c>
       <c r="R6" t="n">
-        <v>6705054</v>
+        <v>6705174</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,17 +1214,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,12 +1244,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Emil Alexandersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Emil Alexandersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 9959-2026 artfynd.xlsx
+++ b/artfynd/A 9959-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112215602</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100764566</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131273722</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131273746</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,8 +1278,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115904308</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>